--- a/gsflow/parameter_data.xlsx
+++ b/gsflow/parameter_data.xlsx
@@ -21,6 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">prep!$A$1:$K$534</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'v1'!$A$1:$H$534</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">v2_unitsConversion!$A$1:$M$548</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -79729,6 +79730,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M548"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
